--- a/DXLibProject_Start/Data/CSV/HealBottleModel.xlsx
+++ b/DXLibProject_Start/Data/CSV/HealBottleModel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{786DCBFC-E081-41AB-B3E2-FB5AFAF3A88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB66A439-C2B5-40D9-B752-09B600B8645D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3030" yWindow="3030" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-225" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>bottlePotionHealth.mv1</t>
+    <t>HealBottle.mv1</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
